--- a/Soluciones_excel.xlsx
+++ b/Soluciones_excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c70834368b779c7c/Documentos/CURSOS UNI 26-1/CONTROL ESTADISTICO DEL PROCESO/PC4_Tello_Patrick/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{85108B73-AD35-4A38-B68A-FD787B415C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{862F44C0-9807-4D5D-BAB2-6B973881A2F6}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{85108B73-AD35-4A38-B68A-FD787B415C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CF7C5A4-1F51-4AC6-B7C4-B512A192506C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{29897C20-D7E8-4588-A092-B9D07C52E4BD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{29897C20-D7E8-4588-A092-B9D07C52E4BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Problema1_XR" sheetId="2" r:id="rId1"/>
@@ -19,13 +19,7 @@
     <sheet name="Problema4_np" sheetId="5" r:id="rId4"/>
     <sheet name="Hoja6" sheetId="6" r:id="rId5"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId6"/>
-    <externalReference r:id="rId7"/>
-    <externalReference r:id="rId8"/>
-    <externalReference r:id="rId9"/>
-  </externalReferences>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -521,9 +515,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="168" formatCode="0.000"/>
-    <numFmt numFmtId="169" formatCode="0.0000"/>
-    <numFmt numFmtId="170" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
@@ -708,17 +702,8 @@
   </cellStyleXfs>
   <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -733,7 +718,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -745,41 +730,35 @@
     <xf numFmtId="2" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -792,6 +771,21 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5341,1066 +5335,8 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Problema1_XR"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="4">
-          <cell r="G4" t="str">
-            <v>X̄ (media)</v>
-          </cell>
-          <cell r="H4" t="str">
-            <v>R (rango)</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5">
-            <v>1</v>
-          </cell>
-          <cell r="G5">
-            <v>45</v>
-          </cell>
-          <cell r="H5">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6">
-            <v>2</v>
-          </cell>
-          <cell r="G6">
-            <v>44.8</v>
-          </cell>
-          <cell r="H6">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7">
-            <v>3</v>
-          </cell>
-          <cell r="G7">
-            <v>45.6</v>
-          </cell>
-          <cell r="H7">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8">
-            <v>4</v>
-          </cell>
-          <cell r="G8">
-            <v>44.6</v>
-          </cell>
-          <cell r="H8">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9">
-            <v>5</v>
-          </cell>
-          <cell r="G9">
-            <v>44.8</v>
-          </cell>
-          <cell r="H9">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10">
-            <v>6</v>
-          </cell>
-          <cell r="G10">
-            <v>46.6</v>
-          </cell>
-          <cell r="H10">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11">
-            <v>7</v>
-          </cell>
-          <cell r="G11">
-            <v>43.6</v>
-          </cell>
-          <cell r="H11">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12">
-            <v>8</v>
-          </cell>
-          <cell r="G12">
-            <v>45.8</v>
-          </cell>
-          <cell r="H12">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13">
-            <v>9</v>
-          </cell>
-          <cell r="G13">
-            <v>45.2</v>
-          </cell>
-          <cell r="H13">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14">
-            <v>10</v>
-          </cell>
-          <cell r="G14">
-            <v>47.6</v>
-          </cell>
-          <cell r="H14">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>11</v>
-          </cell>
-          <cell r="G15">
-            <v>44.2</v>
-          </cell>
-          <cell r="H15">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>12</v>
-          </cell>
-          <cell r="G16">
-            <v>45.6</v>
-          </cell>
-          <cell r="H16">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19" t="str">
-            <v>LC_X</v>
-          </cell>
-          <cell r="B19" t="str">
-            <v>LCS_X</v>
-          </cell>
-          <cell r="C19" t="str">
-            <v>LCI_X</v>
-          </cell>
-          <cell r="D19" t="str">
-            <v>LC_R</v>
-          </cell>
-          <cell r="E19" t="str">
-            <v>LCS_R</v>
-          </cell>
-          <cell r="F19" t="str">
-            <v>LCI_R</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20">
-            <v>45.283333333333339</v>
-          </cell>
-          <cell r="B20">
-            <v>46.822000000000003</v>
-          </cell>
-          <cell r="C20">
-            <v>43.744666666666674</v>
-          </cell>
-          <cell r="D20">
-            <v>2.6666666666666665</v>
-          </cell>
-          <cell r="E20">
-            <v>5.6373333333333324</v>
-          </cell>
-          <cell r="F20">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21">
-            <v>45.283333333333339</v>
-          </cell>
-          <cell r="B21">
-            <v>46.822000000000003</v>
-          </cell>
-          <cell r="C21">
-            <v>43.744666666666674</v>
-          </cell>
-          <cell r="D21">
-            <v>2.6666666666666665</v>
-          </cell>
-          <cell r="E21">
-            <v>5.6373333333333324</v>
-          </cell>
-          <cell r="F21">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22">
-            <v>45.283333333333339</v>
-          </cell>
-          <cell r="B22">
-            <v>46.822000000000003</v>
-          </cell>
-          <cell r="C22">
-            <v>43.744666666666674</v>
-          </cell>
-          <cell r="D22">
-            <v>2.6666666666666665</v>
-          </cell>
-          <cell r="E22">
-            <v>5.6373333333333324</v>
-          </cell>
-          <cell r="F22">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23">
-            <v>45.283333333333339</v>
-          </cell>
-          <cell r="B23">
-            <v>46.822000000000003</v>
-          </cell>
-          <cell r="C23">
-            <v>43.744666666666674</v>
-          </cell>
-          <cell r="D23">
-            <v>2.6666666666666665</v>
-          </cell>
-          <cell r="E23">
-            <v>5.6373333333333324</v>
-          </cell>
-          <cell r="F23">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24">
-            <v>45.283333333333339</v>
-          </cell>
-          <cell r="B24">
-            <v>46.822000000000003</v>
-          </cell>
-          <cell r="C24">
-            <v>43.744666666666674</v>
-          </cell>
-          <cell r="D24">
-            <v>2.6666666666666665</v>
-          </cell>
-          <cell r="E24">
-            <v>5.6373333333333324</v>
-          </cell>
-          <cell r="F24">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25">
-            <v>45.283333333333339</v>
-          </cell>
-          <cell r="B25">
-            <v>46.822000000000003</v>
-          </cell>
-          <cell r="C25">
-            <v>43.744666666666674</v>
-          </cell>
-          <cell r="D25">
-            <v>2.6666666666666665</v>
-          </cell>
-          <cell r="E25">
-            <v>5.6373333333333324</v>
-          </cell>
-          <cell r="F25">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26">
-            <v>45.283333333333339</v>
-          </cell>
-          <cell r="B26">
-            <v>46.822000000000003</v>
-          </cell>
-          <cell r="C26">
-            <v>43.744666666666674</v>
-          </cell>
-          <cell r="D26">
-            <v>2.6666666666666665</v>
-          </cell>
-          <cell r="E26">
-            <v>5.6373333333333324</v>
-          </cell>
-          <cell r="F26">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27">
-            <v>45.283333333333339</v>
-          </cell>
-          <cell r="B27">
-            <v>46.822000000000003</v>
-          </cell>
-          <cell r="C27">
-            <v>43.744666666666674</v>
-          </cell>
-          <cell r="D27">
-            <v>2.6666666666666665</v>
-          </cell>
-          <cell r="E27">
-            <v>5.6373333333333324</v>
-          </cell>
-          <cell r="F27">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28">
-            <v>45.283333333333339</v>
-          </cell>
-          <cell r="B28">
-            <v>46.822000000000003</v>
-          </cell>
-          <cell r="C28">
-            <v>43.744666666666674</v>
-          </cell>
-          <cell r="D28">
-            <v>2.6666666666666665</v>
-          </cell>
-          <cell r="E28">
-            <v>5.6373333333333324</v>
-          </cell>
-          <cell r="F28">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29">
-            <v>45.283333333333339</v>
-          </cell>
-          <cell r="B29">
-            <v>46.822000000000003</v>
-          </cell>
-          <cell r="C29">
-            <v>43.744666666666674</v>
-          </cell>
-          <cell r="D29">
-            <v>2.6666666666666665</v>
-          </cell>
-          <cell r="E29">
-            <v>5.6373333333333324</v>
-          </cell>
-          <cell r="F29">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30">
-            <v>45.283333333333339</v>
-          </cell>
-          <cell r="B30">
-            <v>46.822000000000003</v>
-          </cell>
-          <cell r="C30">
-            <v>43.744666666666674</v>
-          </cell>
-          <cell r="D30">
-            <v>2.6666666666666665</v>
-          </cell>
-          <cell r="E30">
-            <v>5.6373333333333324</v>
-          </cell>
-          <cell r="F30">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31">
-            <v>45.283333333333339</v>
-          </cell>
-          <cell r="B31">
-            <v>46.822000000000003</v>
-          </cell>
-          <cell r="C31">
-            <v>43.744666666666674</v>
-          </cell>
-          <cell r="D31">
-            <v>2.6666666666666665</v>
-          </cell>
-          <cell r="E31">
-            <v>5.6373333333333324</v>
-          </cell>
-          <cell r="F31">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Problema2_u"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="4">
-          <cell r="D4" t="str">
-            <v>u = c/n</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5">
-            <v>1</v>
-          </cell>
-          <cell r="D5">
-            <v>0.06</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6">
-            <v>2</v>
-          </cell>
-          <cell r="D6">
-            <v>4.4444444444444446E-2</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7">
-            <v>3</v>
-          </cell>
-          <cell r="D7">
-            <v>7.2727272727272724E-2</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8">
-            <v>4</v>
-          </cell>
-          <cell r="D8">
-            <v>6.25E-2</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9">
-            <v>5</v>
-          </cell>
-          <cell r="D9">
-            <v>3.8461538461538464E-2</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10">
-            <v>6</v>
-          </cell>
-          <cell r="D10">
-            <v>8.3333333333333329E-2</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11">
-            <v>7</v>
-          </cell>
-          <cell r="D11">
-            <v>6.3829787234042548E-2</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12">
-            <v>8</v>
-          </cell>
-          <cell r="D12">
-            <v>0.08</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13">
-            <v>9</v>
-          </cell>
-          <cell r="D13">
-            <v>4.5454545454545456E-2</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14">
-            <v>10</v>
-          </cell>
-          <cell r="D14">
-            <v>8.6206896551724144E-2</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>11</v>
-          </cell>
-          <cell r="D15">
-            <v>5.6603773584905662E-2</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>12</v>
-          </cell>
-          <cell r="D16">
-            <v>4.0816326530612242E-2</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17">
-            <v>13</v>
-          </cell>
-          <cell r="D17">
-            <v>7.1428571428571425E-2</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18">
-            <v>14</v>
-          </cell>
-          <cell r="D18">
-            <v>5.8823529411764705E-2</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19">
-            <v>15</v>
-          </cell>
-          <cell r="D19">
-            <v>4.3478260869565216E-2</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20">
-            <v>16</v>
-          </cell>
-          <cell r="D20">
-            <v>0.10169491525423729</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21">
-            <v>17</v>
-          </cell>
-          <cell r="D21">
-            <v>5.5555555555555552E-2</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22">
-            <v>18</v>
-          </cell>
-          <cell r="D22">
-            <v>0.06</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25" t="str">
-            <v>LC_u</v>
-          </cell>
-          <cell r="B25" t="str">
-            <v>LCS_u</v>
-          </cell>
-          <cell r="C25" t="str">
-            <v>LCI_u</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26">
-            <v>6.3646170442286945E-2</v>
-          </cell>
-          <cell r="B26">
-            <v>0.16911005870636669</v>
-          </cell>
-          <cell r="C26">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27">
-            <v>6.3646170442286945E-2</v>
-          </cell>
-          <cell r="B27">
-            <v>0.16911005870636669</v>
-          </cell>
-          <cell r="C27">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28">
-            <v>6.3646170442286945E-2</v>
-          </cell>
-          <cell r="B28">
-            <v>0.16911005870636669</v>
-          </cell>
-          <cell r="C28">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29">
-            <v>6.3646170442286945E-2</v>
-          </cell>
-          <cell r="B29">
-            <v>0.16911005870636669</v>
-          </cell>
-          <cell r="C29">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30">
-            <v>6.3646170442286945E-2</v>
-          </cell>
-          <cell r="B30">
-            <v>0.16911005870636669</v>
-          </cell>
-          <cell r="C30">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31">
-            <v>6.3646170442286945E-2</v>
-          </cell>
-          <cell r="B31">
-            <v>0.16911005870636669</v>
-          </cell>
-          <cell r="C31">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32">
-            <v>6.3646170442286945E-2</v>
-          </cell>
-          <cell r="B32">
-            <v>0.16911005870636669</v>
-          </cell>
-          <cell r="C32">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33">
-            <v>6.3646170442286945E-2</v>
-          </cell>
-          <cell r="B33">
-            <v>0.16911005870636669</v>
-          </cell>
-          <cell r="C33">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34">
-            <v>6.3646170442286945E-2</v>
-          </cell>
-          <cell r="B34">
-            <v>0.16911005870636669</v>
-          </cell>
-          <cell r="C34">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35">
-            <v>6.3646170442286945E-2</v>
-          </cell>
-          <cell r="B35">
-            <v>0.16911005870636669</v>
-          </cell>
-          <cell r="C35">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36">
-            <v>6.3646170442286945E-2</v>
-          </cell>
-          <cell r="B36">
-            <v>0.16911005870636669</v>
-          </cell>
-          <cell r="C36">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37">
-            <v>6.3646170442286945E-2</v>
-          </cell>
-          <cell r="B37">
-            <v>0.16911005870636669</v>
-          </cell>
-          <cell r="C37">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38">
-            <v>6.3646170442286945E-2</v>
-          </cell>
-          <cell r="B38">
-            <v>0.16911005870636669</v>
-          </cell>
-          <cell r="C38">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39">
-            <v>6.3646170442286945E-2</v>
-          </cell>
-          <cell r="B39">
-            <v>0.16911005870636669</v>
-          </cell>
-          <cell r="C39">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40">
-            <v>6.3646170442286945E-2</v>
-          </cell>
-          <cell r="B40">
-            <v>0.16911005870636669</v>
-          </cell>
-          <cell r="C40">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41">
-            <v>6.3646170442286945E-2</v>
-          </cell>
-          <cell r="B41">
-            <v>0.16911005870636669</v>
-          </cell>
-          <cell r="C41">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42">
-            <v>6.3646170442286945E-2</v>
-          </cell>
-          <cell r="B42">
-            <v>0.16911005870636669</v>
-          </cell>
-          <cell r="C42">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43">
-            <v>6.3646170442286945E-2</v>
-          </cell>
-          <cell r="B43">
-            <v>0.16911005870636669</v>
-          </cell>
-          <cell r="C43">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Problema3_Capacidad"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="35">
-          <cell r="B35" t="str">
-            <v>Corto plazo</v>
-          </cell>
-          <cell r="C35" t="str">
-            <v>Largo plazo</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36" t="str">
-            <v>Cp / Pp</v>
-          </cell>
-          <cell r="B36">
-            <v>2.1537037037037035</v>
-          </cell>
-          <cell r="C36">
-            <v>1.1111111111111112</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37" t="str">
-            <v>Cpk / Ppk</v>
-          </cell>
-          <cell r="B37">
-            <v>2.0675555555555554</v>
-          </cell>
-          <cell r="C37">
-            <v>1.0666666666666667</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Problema4_np"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="4">
-          <cell r="C4" t="str">
-            <v>np (entregas tardías)</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5">
-            <v>1</v>
-          </cell>
-          <cell r="C5">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6">
-            <v>2</v>
-          </cell>
-          <cell r="C6">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7">
-            <v>3</v>
-          </cell>
-          <cell r="C7">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8">
-            <v>4</v>
-          </cell>
-          <cell r="C8">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9">
-            <v>5</v>
-          </cell>
-          <cell r="C9">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10">
-            <v>6</v>
-          </cell>
-          <cell r="C10">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11">
-            <v>7</v>
-          </cell>
-          <cell r="C11">
-            <v>7</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12">
-            <v>8</v>
-          </cell>
-          <cell r="C12">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13">
-            <v>9</v>
-          </cell>
-          <cell r="C13">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14">
-            <v>10</v>
-          </cell>
-          <cell r="C14">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43" t="str">
-            <v>LC_np</v>
-          </cell>
-          <cell r="B43" t="str">
-            <v>LCS_np</v>
-          </cell>
-          <cell r="C43" t="str">
-            <v>LCI_np</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44">
-            <v>4.0999999999999996</v>
-          </cell>
-          <cell r="B44">
-            <v>9.8548023423919595</v>
-          </cell>
-          <cell r="C44">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="A45">
-            <v>4.0999999999999996</v>
-          </cell>
-          <cell r="B45">
-            <v>9.8548023423919595</v>
-          </cell>
-          <cell r="C45">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="A46">
-            <v>4.0999999999999996</v>
-          </cell>
-          <cell r="B46">
-            <v>9.8548023423919595</v>
-          </cell>
-          <cell r="C46">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="A47">
-            <v>4.0999999999999996</v>
-          </cell>
-          <cell r="B47">
-            <v>9.8548023423919595</v>
-          </cell>
-          <cell r="C47">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="A48">
-            <v>4.0999999999999996</v>
-          </cell>
-          <cell r="B48">
-            <v>9.8548023423919595</v>
-          </cell>
-          <cell r="C48">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="A49">
-            <v>4.0999999999999996</v>
-          </cell>
-          <cell r="B49">
-            <v>9.8548023423919595</v>
-          </cell>
-          <cell r="C49">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="A50">
-            <v>4.0999999999999996</v>
-          </cell>
-          <cell r="B50">
-            <v>9.8548023423919595</v>
-          </cell>
-          <cell r="C50">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="A51">
-            <v>4.0999999999999996</v>
-          </cell>
-          <cell r="B51">
-            <v>9.8548023423919595</v>
-          </cell>
-          <cell r="C51">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="A52">
-            <v>4.0999999999999996</v>
-          </cell>
-          <cell r="B52">
-            <v>9.8548023423919595</v>
-          </cell>
-          <cell r="C52">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="A53">
-            <v>4.0999999999999996</v>
-          </cell>
-          <cell r="B53">
-            <v>9.8548023423919595</v>
-          </cell>
-          <cell r="C53">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6723,917 +5659,917 @@
   <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12" style="2" customWidth="1"/>
-    <col min="2" max="6" width="9" style="2" customWidth="1"/>
-    <col min="7" max="7" width="12" style="2" customWidth="1"/>
-    <col min="8" max="8" width="10" style="2" customWidth="1"/>
-    <col min="9" max="9" width="3" style="2" customWidth="1"/>
-    <col min="10" max="10" width="18" style="2" customWidth="1"/>
-    <col min="11" max="11" width="14" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="8.6328125" style="2"/>
+    <col min="1" max="1" width="12" style="1" customWidth="1"/>
+    <col min="2" max="6" width="9" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10" style="1" customWidth="1"/>
+    <col min="9" max="9" width="3" style="1" customWidth="1"/>
+    <col min="10" max="10" width="18" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.6328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="5"/>
+      <c r="K4" s="28"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" s="6">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="4">
         <v>44</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="4">
         <v>46</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="4">
         <v>45</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="4">
         <v>43</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="4">
         <v>47</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="5">
         <f t="shared" ref="G5:G16" si="0">AVERAGE(B5:F5)</f>
         <v>45</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="5">
         <f t="shared" ref="H5:H16" si="1">MAX(B5:F5)-MIN(B5:F5)</f>
         <v>4</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="7">
         <v>0.57699999999999996</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A6" s="11">
+      <c r="A6" s="8">
         <v>2</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="9">
         <v>45</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="9">
         <v>44</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="9">
         <v>46</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="9">
         <v>45</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="9">
         <v>44</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="10">
         <f t="shared" si="0"/>
         <v>44.8</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="10">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" s="6">
+      <c r="A7" s="3">
         <v>3</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="4">
         <v>46</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="4">
         <v>45</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="4">
         <v>47</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="4">
         <v>44</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="4">
         <v>46</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="5">
         <f t="shared" si="0"/>
         <v>45.6</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="5">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="7">
         <v>2.1139999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="11">
+      <c r="A8" s="8">
         <v>4</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="9">
         <v>43</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="9">
         <v>45</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="9">
         <v>44</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="9">
         <v>46</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="9">
         <v>45</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="10">
         <f t="shared" si="0"/>
         <v>44.6</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="10">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8" s="7">
         <v>2.3260000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="6">
+      <c r="A9" s="3">
         <v>5</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="4">
         <v>45</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="4">
         <v>46</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="4">
         <v>44</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="4">
         <v>45</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="4">
         <v>44</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="5">
         <f t="shared" si="0"/>
         <v>44.8</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="5">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" s="11">
+      <c r="A10" s="8">
         <v>6</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="9">
         <v>47</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="9">
         <v>46</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="9">
         <v>48</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="9">
         <v>45</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="9">
         <v>47</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="10">
         <f t="shared" si="0"/>
         <v>46.6</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="10">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="5"/>
+      <c r="K10" s="28"/>
     </row>
     <row r="11" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="6">
+      <c r="A11" s="3">
         <v>7</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="4">
         <v>44</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="4">
         <v>43</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="4">
         <v>45</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="4">
         <v>44</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="4">
         <v>42</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="5">
         <f t="shared" si="0"/>
         <v>43.6</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="5">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="11">
         <f>AVERAGE(G5:G16)</f>
         <v>45.283333333333339</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="11">
+      <c r="A12" s="8">
         <v>8</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="9">
         <v>46</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="9">
         <v>45</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="9">
         <v>47</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="9">
         <v>46</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="9">
         <v>45</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="10">
         <f t="shared" si="0"/>
         <v>45.8</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="10">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="K12" s="14">
+      <c r="K12" s="11">
         <f>AVERAGE(H5:H16)</f>
         <v>2.6666666666666665</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="6">
+      <c r="A13" s="3">
         <v>9</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="4">
         <v>45</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="4">
         <v>44</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="4">
         <v>46</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="4">
         <v>45</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="4">
         <v>46</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="5">
         <f t="shared" si="0"/>
         <v>45.2</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="5">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="11">
         <f>K11</f>
         <v>45.283333333333339</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="11">
+      <c r="A14" s="8">
         <v>10</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="9">
         <v>48</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="9">
         <v>47</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="9">
         <v>49</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="9">
         <v>48</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="9">
         <v>46</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="10">
         <f t="shared" si="0"/>
         <v>47.6</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="10">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="11">
         <f>K11+K5*K12</f>
         <v>46.822000000000003</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="6">
+      <c r="A15" s="3">
         <v>11</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="4">
         <v>44</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="4">
         <v>45</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="4">
         <v>43</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="4">
         <v>44</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="4">
         <v>45</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="5">
         <f t="shared" si="0"/>
         <v>44.2</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="5">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="J15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="11">
         <f>K11-K5*K12</f>
         <v>43.744666666666674</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="11">
+      <c r="A16" s="8">
         <v>12</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="9">
         <v>46</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="9">
         <v>47</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="9">
         <v>45</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="9">
         <v>46</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="9">
         <v>44</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="10">
         <f t="shared" si="0"/>
         <v>45.6</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="10">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="J16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="11">
         <f>K12</f>
         <v>2.6666666666666665</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="J17" s="9" t="s">
+      <c r="J17" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="K17" s="14">
+      <c r="K17" s="11">
         <f>K7*K12</f>
         <v>5.6373333333333324</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="J18" s="9" t="s">
+      <c r="J18" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="11">
         <f>K6*K12</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="J19" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19" s="11">
         <f>K12/K8</f>
         <v>1.1464603038119805</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A20" s="15">
+      <c r="A20" s="12">
         <f t="shared" ref="A20:A31" si="2">$K$13</f>
         <v>45.283333333333339</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="12">
         <f t="shared" ref="B20:B31" si="3">$K$14</f>
         <v>46.822000000000003</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="12">
         <f t="shared" ref="C20:C31" si="4">$K$15</f>
         <v>43.744666666666674</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="12">
         <f t="shared" ref="D20:D31" si="5">$K$16</f>
         <v>2.6666666666666665</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="12">
         <f t="shared" ref="E20:E31" si="6">$K$17</f>
         <v>5.6373333333333324</v>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="12">
         <f t="shared" ref="F20:F31" si="7">$K$18</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A21" s="15">
+      <c r="A21" s="12">
         <f t="shared" si="2"/>
         <v>45.283333333333339</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="12">
         <f t="shared" si="3"/>
         <v>46.822000000000003</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="12">
         <f t="shared" si="4"/>
         <v>43.744666666666674</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="12">
         <f t="shared" si="5"/>
         <v>2.6666666666666665</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="12">
         <f t="shared" si="6"/>
         <v>5.6373333333333324</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="12">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A22" s="15">
+      <c r="A22" s="12">
         <f t="shared" si="2"/>
         <v>45.283333333333339</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="12">
         <f t="shared" si="3"/>
         <v>46.822000000000003</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="12">
         <f t="shared" si="4"/>
         <v>43.744666666666674</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="12">
         <f t="shared" si="5"/>
         <v>2.6666666666666665</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="12">
         <f t="shared" si="6"/>
         <v>5.6373333333333324</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="12">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A23" s="15">
+      <c r="A23" s="12">
         <f t="shared" si="2"/>
         <v>45.283333333333339</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="12">
         <f t="shared" si="3"/>
         <v>46.822000000000003</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="12">
         <f t="shared" si="4"/>
         <v>43.744666666666674</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="12">
         <f t="shared" si="5"/>
         <v>2.6666666666666665</v>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="12">
         <f t="shared" si="6"/>
         <v>5.6373333333333324</v>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="12">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A24" s="15">
+      <c r="A24" s="12">
         <f t="shared" si="2"/>
         <v>45.283333333333339</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="12">
         <f t="shared" si="3"/>
         <v>46.822000000000003</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="12">
         <f t="shared" si="4"/>
         <v>43.744666666666674</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="12">
         <f t="shared" si="5"/>
         <v>2.6666666666666665</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="12">
         <f t="shared" si="6"/>
         <v>5.6373333333333324</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="12">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A25" s="15">
+      <c r="A25" s="12">
         <f t="shared" si="2"/>
         <v>45.283333333333339</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="12">
         <f t="shared" si="3"/>
         <v>46.822000000000003</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="12">
         <f t="shared" si="4"/>
         <v>43.744666666666674</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="12">
         <f t="shared" si="5"/>
         <v>2.6666666666666665</v>
       </c>
-      <c r="E25" s="15">
+      <c r="E25" s="12">
         <f t="shared" si="6"/>
         <v>5.6373333333333324</v>
       </c>
-      <c r="F25" s="15">
+      <c r="F25" s="12">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A26" s="15">
+      <c r="A26" s="12">
         <f t="shared" si="2"/>
         <v>45.283333333333339</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="12">
         <f t="shared" si="3"/>
         <v>46.822000000000003</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="12">
         <f t="shared" si="4"/>
         <v>43.744666666666674</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="12">
         <f t="shared" si="5"/>
         <v>2.6666666666666665</v>
       </c>
-      <c r="E26" s="15">
+      <c r="E26" s="12">
         <f t="shared" si="6"/>
         <v>5.6373333333333324</v>
       </c>
-      <c r="F26" s="15">
+      <c r="F26" s="12">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A27" s="15">
+      <c r="A27" s="12">
         <f t="shared" si="2"/>
         <v>45.283333333333339</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="12">
         <f t="shared" si="3"/>
         <v>46.822000000000003</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="12">
         <f t="shared" si="4"/>
         <v>43.744666666666674</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="12">
         <f t="shared" si="5"/>
         <v>2.6666666666666665</v>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="12">
         <f t="shared" si="6"/>
         <v>5.6373333333333324</v>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="12">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A28" s="15">
+      <c r="A28" s="12">
         <f t="shared" si="2"/>
         <v>45.283333333333339</v>
       </c>
-      <c r="B28" s="15">
+      <c r="B28" s="12">
         <f t="shared" si="3"/>
         <v>46.822000000000003</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="12">
         <f t="shared" si="4"/>
         <v>43.744666666666674</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="12">
         <f t="shared" si="5"/>
         <v>2.6666666666666665</v>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="12">
         <f t="shared" si="6"/>
         <v>5.6373333333333324</v>
       </c>
-      <c r="F28" s="15">
+      <c r="F28" s="12">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A29" s="15">
+      <c r="A29" s="12">
         <f t="shared" si="2"/>
         <v>45.283333333333339</v>
       </c>
-      <c r="B29" s="15">
+      <c r="B29" s="12">
         <f t="shared" si="3"/>
         <v>46.822000000000003</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="12">
         <f t="shared" si="4"/>
         <v>43.744666666666674</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="12">
         <f t="shared" si="5"/>
         <v>2.6666666666666665</v>
       </c>
-      <c r="E29" s="15">
+      <c r="E29" s="12">
         <f t="shared" si="6"/>
         <v>5.6373333333333324</v>
       </c>
-      <c r="F29" s="15">
+      <c r="F29" s="12">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A30" s="15">
+      <c r="A30" s="12">
         <f t="shared" si="2"/>
         <v>45.283333333333339</v>
       </c>
-      <c r="B30" s="15">
+      <c r="B30" s="12">
         <f t="shared" si="3"/>
         <v>46.822000000000003</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="12">
         <f t="shared" si="4"/>
         <v>43.744666666666674</v>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="12">
         <f t="shared" si="5"/>
         <v>2.6666666666666665</v>
       </c>
-      <c r="E30" s="15">
+      <c r="E30" s="12">
         <f t="shared" si="6"/>
         <v>5.6373333333333324</v>
       </c>
-      <c r="F30" s="15">
+      <c r="F30" s="12">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A31" s="15">
+      <c r="A31" s="12">
         <f t="shared" si="2"/>
         <v>45.283333333333339</v>
       </c>
-      <c r="B31" s="15">
+      <c r="B31" s="12">
         <f t="shared" si="3"/>
         <v>46.822000000000003</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="12">
         <f t="shared" si="4"/>
         <v>43.744666666666674</v>
       </c>
-      <c r="D31" s="15">
+      <c r="D31" s="12">
         <f t="shared" si="5"/>
         <v>2.6666666666666665</v>
       </c>
-      <c r="E31" s="15">
+      <c r="E31" s="12">
         <f t="shared" si="6"/>
         <v>5.6373333333333324</v>
       </c>
-      <c r="F31" s="15">
+      <c r="F31" s="12">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
     </row>
     <row r="34" spans="1:8" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
     </row>
     <row r="35" spans="1:8" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
     </row>
     <row r="36" spans="1:8" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
     </row>
     <row r="37" spans="1:8" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
     </row>
     <row r="38" spans="1:8" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A34:H34"/>
     <mergeCell ref="A35:H35"/>
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A37:H37"/>
     <mergeCell ref="A38:H38"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:G16">
     <cfRule type="cellIs" dxfId="5" priority="1" operator="greaterThan">
@@ -7654,745 +6590,751 @@
   <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16" style="2" customWidth="1"/>
-    <col min="3" max="4" width="10" style="2" customWidth="1"/>
-    <col min="5" max="5" width="3" style="2" customWidth="1"/>
-    <col min="6" max="6" width="22.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="3" style="2" customWidth="1"/>
-    <col min="10" max="10" width="20" style="2" customWidth="1"/>
-    <col min="11" max="11" width="14" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="8.6328125" style="2"/>
+    <col min="1" max="1" width="8" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10" style="1" customWidth="1"/>
+    <col min="5" max="5" width="3" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="3" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.6328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="G4" s="5"/>
+      <c r="G4" s="28"/>
     </row>
     <row r="5" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="6">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="4">
         <v>50</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="4">
         <v>3</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="13">
         <f t="shared" ref="D5:D22" si="0">C5/B5</f>
         <v>0.06</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="14">
         <f>SUM(C5:C22)</f>
         <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="11">
+      <c r="A6" s="8">
         <v>2</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="9">
         <v>45</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="9">
         <v>2</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="15">
         <f t="shared" si="0"/>
         <v>4.4444444444444446E-2</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="14">
         <f>SUM(B5:B22)</f>
         <v>927</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="6">
+      <c r="A7" s="3">
         <v>3</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="4">
         <v>55</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="4">
         <v>4</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="13">
         <f t="shared" si="0"/>
         <v>7.2727272727272724E-2</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="14">
         <f>COUNT(A5:A22)</f>
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="11">
+      <c r="A8" s="8">
         <v>4</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="9">
         <v>48</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="9">
         <v>3</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="15">
         <f t="shared" si="0"/>
         <v>6.25E-2</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="16">
         <f>G5/G6</f>
         <v>6.3646170442286945E-2</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="6">
+      <c r="A9" s="3">
         <v>5</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="4">
         <v>52</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="4">
         <v>2</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="13">
         <f t="shared" si="0"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="16">
         <f>G6/G7</f>
         <v>51.5</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="11">
+      <c r="A10" s="8">
         <v>6</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="9">
         <v>60</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="9">
         <v>5</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="15">
         <f t="shared" si="0"/>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="17">
         <f>SQRT(G8/G9)</f>
         <v>3.5154629421359919E-2</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="6">
+      <c r="A11" s="3">
         <v>7</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="4">
         <v>47</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="4">
         <v>3</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="13">
         <f t="shared" si="0"/>
         <v>6.3829787234042548E-2</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="16">
         <f>G8+3*G10</f>
         <v>0.16911005870636669</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="11">
+      <c r="A12" s="8">
         <v>8</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="9">
         <v>50</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="9">
         <v>4</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="15">
         <f t="shared" si="0"/>
         <v>0.08</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="16">
         <f>MAX(0,G8-3*G10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="6">
+      <c r="A13" s="3">
         <v>9</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="4">
         <v>44</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="4">
         <v>2</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="13">
         <f t="shared" si="0"/>
         <v>4.5454545454545456E-2</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="11">
+      <c r="A14" s="8">
         <v>10</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="9">
         <v>58</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="9">
         <v>5</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="15">
         <f t="shared" si="0"/>
         <v>8.6206896551724144E-2</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="6">
+      <c r="A15" s="3">
         <v>11</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="4">
         <v>53</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="4">
         <v>3</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="13">
         <f t="shared" si="0"/>
         <v>5.6603773584905662E-2</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="11">
+      <c r="A16" s="8">
         <v>12</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="9">
         <v>49</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="9">
         <v>2</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="15">
         <f t="shared" si="0"/>
         <v>4.0816326530612242E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="6">
+      <c r="A17" s="3">
         <v>13</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="4">
         <v>56</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="4">
         <v>4</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="13">
         <f t="shared" si="0"/>
         <v>7.1428571428571425E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="11">
+      <c r="A18" s="8">
         <v>14</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="9">
         <v>51</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="9">
         <v>3</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="15">
         <f t="shared" si="0"/>
         <v>5.8823529411764705E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="6">
+      <c r="A19" s="3">
         <v>15</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="4">
         <v>46</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="4">
         <v>2</v>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="13">
         <f t="shared" si="0"/>
         <v>4.3478260869565216E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="11">
+      <c r="A20" s="8">
         <v>16</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="9">
         <v>59</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="9">
         <v>6</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="15">
         <f t="shared" si="0"/>
         <v>0.10169491525423729</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="6">
+      <c r="A21" s="3">
         <v>17</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="4">
         <v>54</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="4">
         <v>3</v>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="13">
         <f t="shared" si="0"/>
         <v>5.5555555555555552E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="11">
+      <c r="A22" s="8">
         <v>18</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="9">
         <v>50</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="9">
         <v>3</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="15">
         <f t="shared" si="0"/>
         <v>0.06</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B23" s="2">
+      <c r="B23" s="1">
         <f>AVERAGE(B5:B22)</f>
         <v>51.5</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="2" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="22">
+      <c r="A26" s="18">
         <f t="shared" ref="A26:A43" si="1">$G$8</f>
         <v>6.3646170442286945E-2</v>
       </c>
-      <c r="B26" s="22">
+      <c r="B26" s="18">
         <f t="shared" ref="B26:B43" si="2">$G$11</f>
         <v>0.16911005870636669</v>
       </c>
-      <c r="C26" s="22">
+      <c r="C26" s="18">
         <f t="shared" ref="C26:C43" si="3">$G$12</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="22">
+      <c r="A27" s="18">
         <f t="shared" si="1"/>
         <v>6.3646170442286945E-2</v>
       </c>
-      <c r="B27" s="22">
+      <c r="B27" s="18">
         <f t="shared" si="2"/>
         <v>0.16911005870636669</v>
       </c>
-      <c r="C27" s="22">
+      <c r="C27" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="22">
+      <c r="A28" s="18">
         <f t="shared" si="1"/>
         <v>6.3646170442286945E-2</v>
       </c>
-      <c r="B28" s="22">
+      <c r="B28" s="18">
         <f t="shared" si="2"/>
         <v>0.16911005870636669</v>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="22">
+      <c r="A29" s="18">
         <f t="shared" si="1"/>
         <v>6.3646170442286945E-2</v>
       </c>
-      <c r="B29" s="22">
+      <c r="B29" s="18">
         <f t="shared" si="2"/>
         <v>0.16911005870636669</v>
       </c>
-      <c r="C29" s="22">
+      <c r="C29" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="22">
+      <c r="A30" s="18">
         <f t="shared" si="1"/>
         <v>6.3646170442286945E-2</v>
       </c>
-      <c r="B30" s="22">
+      <c r="B30" s="18">
         <f t="shared" si="2"/>
         <v>0.16911005870636669</v>
       </c>
-      <c r="C30" s="22">
+      <c r="C30" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="22">
+      <c r="A31" s="18">
         <f t="shared" si="1"/>
         <v>6.3646170442286945E-2</v>
       </c>
-      <c r="B31" s="22">
+      <c r="B31" s="18">
         <f t="shared" si="2"/>
         <v>0.16911005870636669</v>
       </c>
-      <c r="C31" s="22">
+      <c r="C31" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="22">
+      <c r="A32" s="18">
         <f t="shared" si="1"/>
         <v>6.3646170442286945E-2</v>
       </c>
-      <c r="B32" s="22">
+      <c r="B32" s="18">
         <f t="shared" si="2"/>
         <v>0.16911005870636669</v>
       </c>
-      <c r="C32" s="22">
+      <c r="C32" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="22">
+      <c r="A33" s="18">
         <f t="shared" si="1"/>
         <v>6.3646170442286945E-2</v>
       </c>
-      <c r="B33" s="22">
+      <c r="B33" s="18">
         <f t="shared" si="2"/>
         <v>0.16911005870636669</v>
       </c>
-      <c r="C33" s="22">
+      <c r="C33" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="22">
+      <c r="A34" s="18">
         <f t="shared" si="1"/>
         <v>6.3646170442286945E-2</v>
       </c>
-      <c r="B34" s="22">
+      <c r="B34" s="18">
         <f t="shared" si="2"/>
         <v>0.16911005870636669</v>
       </c>
-      <c r="C34" s="22">
+      <c r="C34" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="22">
+      <c r="A35" s="18">
         <f t="shared" si="1"/>
         <v>6.3646170442286945E-2</v>
       </c>
-      <c r="B35" s="22">
+      <c r="B35" s="18">
         <f t="shared" si="2"/>
         <v>0.16911005870636669</v>
       </c>
-      <c r="C35" s="22">
+      <c r="C35" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="22">
+      <c r="A36" s="18">
         <f t="shared" si="1"/>
         <v>6.3646170442286945E-2</v>
       </c>
-      <c r="B36" s="22">
+      <c r="B36" s="18">
         <f t="shared" si="2"/>
         <v>0.16911005870636669</v>
       </c>
-      <c r="C36" s="22">
+      <c r="C36" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="22">
+      <c r="A37" s="18">
         <f t="shared" si="1"/>
         <v>6.3646170442286945E-2</v>
       </c>
-      <c r="B37" s="22">
+      <c r="B37" s="18">
         <f t="shared" si="2"/>
         <v>0.16911005870636669</v>
       </c>
-      <c r="C37" s="22">
+      <c r="C37" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="22">
+      <c r="A38" s="18">
         <f t="shared" si="1"/>
         <v>6.3646170442286945E-2</v>
       </c>
-      <c r="B38" s="22">
+      <c r="B38" s="18">
         <f t="shared" si="2"/>
         <v>0.16911005870636669</v>
       </c>
-      <c r="C38" s="22">
+      <c r="C38" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="22">
+      <c r="A39" s="18">
         <f t="shared" si="1"/>
         <v>6.3646170442286945E-2</v>
       </c>
-      <c r="B39" s="22">
+      <c r="B39" s="18">
         <f t="shared" si="2"/>
         <v>0.16911005870636669</v>
       </c>
-      <c r="C39" s="22">
+      <c r="C39" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="22">
+      <c r="A40" s="18">
         <f t="shared" si="1"/>
         <v>6.3646170442286945E-2</v>
       </c>
-      <c r="B40" s="22">
+      <c r="B40" s="18">
         <f t="shared" si="2"/>
         <v>0.16911005870636669</v>
       </c>
-      <c r="C40" s="22">
+      <c r="C40" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="22">
+      <c r="A41" s="18">
         <f t="shared" si="1"/>
         <v>6.3646170442286945E-2</v>
       </c>
-      <c r="B41" s="22">
+      <c r="B41" s="18">
         <f t="shared" si="2"/>
         <v>0.16911005870636669</v>
       </c>
-      <c r="C41" s="22">
+      <c r="C41" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="22">
+      <c r="A42" s="18">
         <f t="shared" si="1"/>
         <v>6.3646170442286945E-2</v>
       </c>
-      <c r="B42" s="22">
+      <c r="B42" s="18">
         <f t="shared" si="2"/>
         <v>0.16911005870636669</v>
       </c>
-      <c r="C42" s="22">
+      <c r="C42" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="22">
+      <c r="A43" s="18">
         <f t="shared" si="1"/>
         <v>6.3646170442286945E-2</v>
       </c>
-      <c r="B43" s="22">
+      <c r="B43" s="18">
         <f t="shared" si="2"/>
         <v>0.16911005870636669</v>
       </c>
-      <c r="C43" s="22">
+      <c r="C43" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
     </row>
     <row r="46" spans="1:4" ht="37.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="16" t="s">
+      <c r="A46" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="B46" s="16"/>
-      <c r="C46" s="16"/>
-      <c r="D46" s="16"/>
+      <c r="B46" s="25"/>
+      <c r="C46" s="25"/>
+      <c r="D46" s="25"/>
     </row>
     <row r="47" spans="1:4" ht="37.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="16" t="s">
+      <c r="A47" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="B47" s="16"/>
-      <c r="C47" s="16"/>
-      <c r="D47" s="16"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="25"/>
     </row>
     <row r="48" spans="1:4" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="16" t="s">
+      <c r="A48" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="B48" s="16"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="25"/>
+      <c r="D48" s="25"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
+      <c r="B50" s="28"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
     </row>
     <row r="51" spans="1:4" ht="37.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="16" t="s">
+      <c r="A51" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="16"/>
-      <c r="C51" s="16"/>
-      <c r="D51" s="16"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="25"/>
     </row>
     <row r="52" spans="1:4" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="16" t="s">
+      <c r="A52" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="B52" s="16"/>
-      <c r="C52" s="16"/>
-      <c r="D52" s="16"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="25"/>
+      <c r="D52" s="25"/>
     </row>
     <row r="53" spans="1:4" ht="37.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="16" t="s">
+      <c r="A53" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="B53" s="16"/>
-      <c r="C53" s="16"/>
-      <c r="D53" s="16"/>
+      <c r="B53" s="25"/>
+      <c r="C53" s="25"/>
+      <c r="D53" s="25"/>
     </row>
     <row r="54" spans="1:4" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="16" t="s">
+      <c r="A54" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="B54" s="16"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="16"/>
+      <c r="B54" s="25"/>
+      <c r="C54" s="25"/>
+      <c r="D54" s="25"/>
     </row>
     <row r="55" spans="1:4" ht="37.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="16" t="s">
+      <c r="A55" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="B55" s="16"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="16"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="25"/>
+      <c r="D55" s="25"/>
     </row>
     <row r="56" spans="1:4" ht="37.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="16" t="s">
+      <c r="A56" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="B56" s="16"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="16"/>
+      <c r="B56" s="25"/>
+      <c r="C56" s="25"/>
+      <c r="D56" s="25"/>
     </row>
     <row r="57" spans="1:4" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="16" t="s">
+      <c r="A57" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="B57" s="16"/>
-      <c r="C57" s="16"/>
-      <c r="D57" s="16"/>
+      <c r="B57" s="25"/>
+      <c r="C57" s="25"/>
+      <c r="D57" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A46:D46"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A57:D57"/>
@@ -8402,12 +7344,6 @@
     <mergeCell ref="A52:D52"/>
     <mergeCell ref="A53:D53"/>
     <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="A47:D47"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D22">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
@@ -8428,530 +7364,526 @@
   <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22" style="2" customWidth="1"/>
-    <col min="5" max="6" width="14" style="2" customWidth="1"/>
-    <col min="7" max="7" width="3" style="2" customWidth="1"/>
-    <col min="8" max="8" width="22" style="2" customWidth="1"/>
-    <col min="9" max="10" width="14" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="8.6328125" style="2"/>
+    <col min="1" max="1" width="30" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22" style="1" customWidth="1"/>
+    <col min="5" max="6" width="14" style="1" customWidth="1"/>
+    <col min="7" max="7" width="3" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22" style="1" customWidth="1"/>
+    <col min="9" max="10" width="14" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.6328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="D4" s="5" t="s">
+      <c r="B4" s="28"/>
+      <c r="D4" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="H4" s="5" t="s">
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="H4" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
     </row>
     <row r="5" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="19">
         <v>-0.5</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="16">
         <f>B9/B10</f>
         <v>7.7386070507308682E-2</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="I5" s="20">
+      <c r="I5" s="16">
         <f>B11</f>
         <v>0.15</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="19">
         <v>0.5</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="16">
         <f>(B6-B5)/(6*E5)</f>
         <v>2.1537037037037035</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="16">
         <f>(B6-B5)/(6*B11)</f>
         <v>1.1111111111111112</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="16">
         <f>(B6-B8)/(3*E5)</f>
         <v>2.0675555555555554</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="16">
         <f>(B6-B8)/(3*B11)</f>
         <v>1.0666666666666667</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="19">
         <v>0.02</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="16">
         <f>(B8-B5)/(3*E5)</f>
         <v>2.239851851851852</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="I8" s="20">
+      <c r="I8" s="16">
         <f>(B8-B5)/(3*B11)</f>
         <v>1.1555555555555557</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="19">
         <v>0.18</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="16">
         <f>MIN(E7,E8)</f>
         <v>2.0675555555555554</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="16">
         <f>MIN(I7,I8)</f>
         <v>1.0666666666666667</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="19">
         <v>2.3260000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="19">
         <v>0.15</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="2" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="13">
         <f>E6</f>
         <v>2.1537037037037035</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="13">
         <f>I6</f>
         <v>1.1111111111111112</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="13">
         <f>B14-C14</f>
         <v>1.0425925925925923</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="15">
         <f>E9</f>
         <v>2.0675555555555554</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="15">
         <f>I9</f>
         <v>1.0666666666666667</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="15">
         <f>B15-C15</f>
         <v>1.0008888888888887</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="25"/>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="25"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="25"/>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25"/>
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="16" t="s">
+      <c r="A30" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="25"/>
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="25"/>
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="16" t="s">
+      <c r="A32" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="25"/>
     </row>
     <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="16"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="25"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="2" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B36" s="17">
+      <c r="B36" s="13">
         <f>E6</f>
         <v>2.1537037037037035</v>
       </c>
-      <c r="C36" s="17">
+      <c r="C36" s="13">
         <f>I6</f>
         <v>1.1111111111111112</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B37" s="17">
+      <c r="B37" s="13">
         <f>E9</f>
         <v>2.0675555555555554</v>
       </c>
-      <c r="C37" s="17">
+      <c r="C37" s="13">
         <f>I9</f>
         <v>1.0666666666666667</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="A33:J33"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="H4:J4"/>
     <mergeCell ref="A28:J28"/>
     <mergeCell ref="A17:J17"/>
     <mergeCell ref="A18:J18"/>
@@ -8959,12 +7891,16 @@
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A21:J21"/>
     <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A33:J33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -8977,612 +7913,630 @@
   <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9" style="2" customWidth="1"/>
-    <col min="2" max="2" width="22" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14" style="2" customWidth="1"/>
-    <col min="6" max="6" width="3" style="2" customWidth="1"/>
-    <col min="7" max="7" width="30" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="8.6328125" style="2"/>
+    <col min="1" max="1" width="9" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14" style="1" customWidth="1"/>
+    <col min="6" max="6" width="3" style="1" customWidth="1"/>
+    <col min="7" max="7" width="30" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.6328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="F4" s="5"/>
+      <c r="F4" s="28"/>
     </row>
     <row r="5" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="6">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="4">
         <v>40</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="4">
         <v>3</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="14">
         <f>SUM(C5:C14)</f>
         <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="11">
+      <c r="A6" s="8">
         <v>2</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="9">
         <v>40</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="9">
         <v>5</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="14">
         <f>SUM(B5:B14)</f>
         <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="6">
+      <c r="A7" s="3">
         <v>3</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="4">
         <v>40</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="4">
         <v>2</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="14">
         <f>COUNT(A5:A14)</f>
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="11">
+      <c r="A8" s="8">
         <v>4</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="9">
         <v>40</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="9">
         <v>6</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="16">
         <f>E5/E6</f>
         <v>0.10249999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="6">
+      <c r="A9" s="3">
         <v>5</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="4">
         <v>40</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="4">
         <v>4</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="16">
         <f>E6/E7*E8</f>
         <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="11">
+      <c r="A10" s="8">
         <v>6</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="9">
         <v>40</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="9">
         <v>3</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="16">
         <f>SQRT(E9*(1-E8))</f>
         <v>1.9182674474639869</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="6">
+      <c r="A11" s="3">
         <v>7</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="4">
         <v>40</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="4">
         <v>7</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="16">
         <f>E9+3*E10</f>
         <v>9.8548023423919595</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="11">
+      <c r="A12" s="8">
         <v>8</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="9">
         <v>40</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="9">
         <v>2</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="16">
         <f>MAX(0,E9-3*E10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="6">
+      <c r="A13" s="3">
         <v>9</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="4">
         <v>40</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="4">
         <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="11">
+      <c r="A14" s="8">
         <v>10</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="9">
         <v>40</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
     </row>
     <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
     </row>
     <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
     </row>
     <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
     </row>
     <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
     </row>
     <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="25" t="s">
         <v>138</v>
       </c>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="16"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
+      <c r="A30" s="25"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
     </row>
     <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
     </row>
     <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="B32" s="25"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
     </row>
     <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="25" t="s">
+      <c r="A33" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="B33" s="25"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="25" t="s">
+      <c r="A34" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
     </row>
     <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="25" t="s">
+      <c r="A35" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
     </row>
     <row r="38" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="25" t="s">
         <v>146</v>
       </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
     </row>
     <row r="39" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="16" t="s">
+      <c r="A39" s="25" t="s">
         <v>147</v>
       </c>
-      <c r="B39" s="16"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
     </row>
     <row r="40" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="16" t="s">
+      <c r="A40" s="25" t="s">
         <v>148</v>
       </c>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="2" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44" s="22">
+      <c r="A44" s="18">
         <f t="shared" ref="A44:A53" si="0">$E$9</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="B44" s="22">
+      <c r="B44" s="18">
         <f t="shared" ref="B44:B53" si="1">$E$11</f>
         <v>9.8548023423919595</v>
       </c>
-      <c r="C44" s="22">
+      <c r="C44" s="18">
         <f t="shared" ref="C44:C53" si="2">$E$12</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" s="22">
+      <c r="A45" s="18">
         <f t="shared" si="0"/>
         <v>4.0999999999999996</v>
       </c>
-      <c r="B45" s="22">
+      <c r="B45" s="18">
         <f t="shared" si="1"/>
         <v>9.8548023423919595</v>
       </c>
-      <c r="C45" s="22">
+      <c r="C45" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A46" s="22">
+      <c r="A46" s="18">
         <f t="shared" si="0"/>
         <v>4.0999999999999996</v>
       </c>
-      <c r="B46" s="22">
+      <c r="B46" s="18">
         <f t="shared" si="1"/>
         <v>9.8548023423919595</v>
       </c>
-      <c r="C46" s="22">
+      <c r="C46" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" s="22">
+      <c r="A47" s="18">
         <f t="shared" si="0"/>
         <v>4.0999999999999996</v>
       </c>
-      <c r="B47" s="22">
+      <c r="B47" s="18">
         <f t="shared" si="1"/>
         <v>9.8548023423919595</v>
       </c>
-      <c r="C47" s="22">
+      <c r="C47" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A48" s="22">
+      <c r="A48" s="18">
         <f t="shared" si="0"/>
         <v>4.0999999999999996</v>
       </c>
-      <c r="B48" s="22">
+      <c r="B48" s="18">
         <f t="shared" si="1"/>
         <v>9.8548023423919595</v>
       </c>
-      <c r="C48" s="22">
+      <c r="C48" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" s="22">
+      <c r="A49" s="18">
         <f t="shared" si="0"/>
         <v>4.0999999999999996</v>
       </c>
-      <c r="B49" s="22">
+      <c r="B49" s="18">
         <f t="shared" si="1"/>
         <v>9.8548023423919595</v>
       </c>
-      <c r="C49" s="22">
+      <c r="C49" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" s="22">
+      <c r="A50" s="18">
         <f t="shared" si="0"/>
         <v>4.0999999999999996</v>
       </c>
-      <c r="B50" s="22">
+      <c r="B50" s="18">
         <f t="shared" si="1"/>
         <v>9.8548023423919595</v>
       </c>
-      <c r="C50" s="22">
+      <c r="C50" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" s="22">
+      <c r="A51" s="18">
         <f t="shared" si="0"/>
         <v>4.0999999999999996</v>
       </c>
-      <c r="B51" s="22">
+      <c r="B51" s="18">
         <f t="shared" si="1"/>
         <v>9.8548023423919595</v>
       </c>
-      <c r="C51" s="22">
+      <c r="C51" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" s="22">
+      <c r="A52" s="18">
         <f t="shared" si="0"/>
         <v>4.0999999999999996</v>
       </c>
-      <c r="B52" s="22">
+      <c r="B52" s="18">
         <f t="shared" si="1"/>
         <v>9.8548023423919595</v>
       </c>
-      <c r="C52" s="22">
+      <c r="C52" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="22">
+      <c r="A53" s="18">
         <f t="shared" si="0"/>
         <v>4.0999999999999996</v>
       </c>
-      <c r="B53" s="22">
+      <c r="B53" s="18">
         <f t="shared" si="1"/>
         <v>9.8548023423919595</v>
       </c>
-      <c r="C53" s="22">
+      <c r="C53" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A33:G33"/>
     <mergeCell ref="A34:G34"/>
@@ -9590,24 +8544,6 @@
     <mergeCell ref="A37:G37"/>
     <mergeCell ref="A38:G38"/>
     <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A19:G19"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:C14">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
@@ -9629,1110 +8565,1110 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="21" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="26">
+      <c r="A2" s="21">
         <v>1</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="22" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="26">
+      <c r="A3" s="21">
         <v>2</v>
       </c>
-      <c r="B3" s="28">
+      <c r="B3" s="23">
         <v>1</v>
       </c>
-      <c r="C3" s="28">
+      <c r="C3" s="23">
         <v>-0.29499999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="26">
+      <c r="A4" s="21">
         <v>3</v>
       </c>
-      <c r="B4" s="28">
+      <c r="B4" s="23">
         <v>1</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="24">
         <v>-0.25</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="26">
+      <c r="A5" s="21">
         <v>4</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="23">
         <v>1</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="23">
         <v>-0.20499999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="26">
+      <c r="A6" s="21">
         <v>5</v>
       </c>
-      <c r="B6" s="28">
+      <c r="B6" s="23">
         <v>1</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="23">
         <v>-0.16</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="26">
+      <c r="A7" s="21">
         <v>6</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="23">
         <v>1</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="23">
         <v>-0.115</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="26">
+      <c r="A8" s="21">
         <v>7</v>
       </c>
-      <c r="B8" s="28">
+      <c r="B8" s="23">
         <v>2</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="23">
         <v>-0.2762</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="26">
+      <c r="A9" s="21">
         <v>8</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="23">
         <v>2</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="23">
         <v>-0.23130000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="26">
+      <c r="A10" s="21">
         <v>9</v>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="23">
         <v>2</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="23">
         <v>-0.18629999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="26">
+      <c r="A11" s="21">
         <v>10</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="23">
         <v>2</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="23">
         <v>-0.14130000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="26">
+      <c r="A12" s="21">
         <v>11</v>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="23">
         <v>2</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="23">
         <v>-9.6299999999999997E-2</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="26">
+      <c r="A13" s="21">
         <v>12</v>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="23">
         <v>3</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="23">
         <v>-0.25750000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="26">
+      <c r="A14" s="21">
         <v>13</v>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="23">
         <v>3</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="23">
         <v>-0.21249999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="26">
+      <c r="A15" s="21">
         <v>14</v>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="23">
         <v>3</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="23">
         <v>-0.16750000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="26">
+      <c r="A16" s="21">
         <v>15</v>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="23">
         <v>3</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="23">
         <v>-0.1225</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="26">
+      <c r="A17" s="21">
         <v>16</v>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="23">
         <v>3</v>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="23">
         <v>-7.7499999999999999E-2</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="26">
+      <c r="A18" s="21">
         <v>17</v>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="23">
         <v>4</v>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="23">
         <v>-0.23880000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="26">
+      <c r="A19" s="21">
         <v>18</v>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="23">
         <v>4</v>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="23">
         <v>-0.1938</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="26">
+      <c r="A20" s="21">
         <v>19</v>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="23">
         <v>4</v>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="23">
         <v>-0.14879999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="26">
+      <c r="A21" s="21">
         <v>20</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="23">
         <v>4</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="23">
         <v>-0.1038</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="26">
+      <c r="A22" s="21">
         <v>21</v>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="23">
         <v>4</v>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="23">
         <v>-5.8799999999999998E-2</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="26">
+      <c r="A23" s="21">
         <v>22</v>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="23">
         <v>5</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="23">
         <v>-0.22</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="26">
+      <c r="A24" s="21">
         <v>23</v>
       </c>
-      <c r="B24" s="28">
+      <c r="B24" s="23">
         <v>5</v>
       </c>
-      <c r="C24" s="28">
+      <c r="C24" s="23">
         <v>-0.17499999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="26">
+      <c r="A25" s="21">
         <v>24</v>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="23">
         <v>5</v>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="23">
         <v>-0.13</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="26">
+      <c r="A26" s="21">
         <v>25</v>
       </c>
-      <c r="B26" s="28">
+      <c r="B26" s="23">
         <v>5</v>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="23">
         <v>-8.5000000000000006E-2</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="26">
+      <c r="A27" s="21">
         <v>26</v>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="23">
         <v>5</v>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="23">
         <v>-0.04</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="26">
+      <c r="A28" s="21">
         <v>27</v>
       </c>
-      <c r="B28" s="28">
+      <c r="B28" s="23">
         <v>6</v>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="23">
         <v>-0.20119999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="26">
+      <c r="A29" s="21">
         <v>28</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="23">
         <v>6</v>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="23">
         <v>-0.15620000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="26">
+      <c r="A30" s="21">
         <v>29</v>
       </c>
-      <c r="B30" s="28">
+      <c r="B30" s="23">
         <v>6</v>
       </c>
-      <c r="C30" s="28">
+      <c r="C30" s="23">
         <v>-0.1113</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="26">
+      <c r="A31" s="21">
         <v>30</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="23">
         <v>6</v>
       </c>
-      <c r="C31" s="28">
+      <c r="C31" s="23">
         <v>-6.6299999999999998E-2</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="26">
+      <c r="A32" s="21">
         <v>31</v>
       </c>
-      <c r="B32" s="28">
+      <c r="B32" s="23">
         <v>6</v>
       </c>
-      <c r="C32" s="28">
+      <c r="C32" s="23">
         <v>-2.1299999999999999E-2</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="26">
+      <c r="A33" s="21">
         <v>32</v>
       </c>
-      <c r="B33" s="28">
+      <c r="B33" s="23">
         <v>7</v>
       </c>
-      <c r="C33" s="28">
+      <c r="C33" s="23">
         <v>-0.1825</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="26">
+      <c r="A34" s="21">
         <v>33</v>
       </c>
-      <c r="B34" s="28">
+      <c r="B34" s="23">
         <v>7</v>
       </c>
-      <c r="C34" s="28">
+      <c r="C34" s="23">
         <v>-0.13750000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="26">
+      <c r="A35" s="21">
         <v>34</v>
       </c>
-      <c r="B35" s="28">
+      <c r="B35" s="23">
         <v>7</v>
       </c>
-      <c r="C35" s="28">
+      <c r="C35" s="23">
         <v>-9.2499999999999999E-2</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="26">
+      <c r="A36" s="21">
         <v>35</v>
       </c>
-      <c r="B36" s="28">
+      <c r="B36" s="23">
         <v>7</v>
       </c>
-      <c r="C36" s="28">
+      <c r="C36" s="23">
         <v>-4.7500000000000001E-2</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="26">
+      <c r="A37" s="21">
         <v>36</v>
       </c>
-      <c r="B37" s="28">
+      <c r="B37" s="23">
         <v>7</v>
       </c>
-      <c r="C37" s="28">
+      <c r="C37" s="23">
         <v>-2.5000000000000001E-3</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="26">
+      <c r="A38" s="21">
         <v>37</v>
       </c>
-      <c r="B38" s="28">
+      <c r="B38" s="23">
         <v>8</v>
       </c>
-      <c r="C38" s="28">
+      <c r="C38" s="23">
         <v>-0.1638</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="26">
+      <c r="A39" s="21">
         <v>38</v>
       </c>
-      <c r="B39" s="28">
+      <c r="B39" s="23">
         <v>8</v>
       </c>
-      <c r="C39" s="28">
+      <c r="C39" s="23">
         <v>-0.1187</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="26">
+      <c r="A40" s="21">
         <v>39</v>
       </c>
-      <c r="B40" s="28">
+      <c r="B40" s="23">
         <v>8</v>
       </c>
-      <c r="C40" s="28">
+      <c r="C40" s="23">
         <v>-7.3700000000000002E-2</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="26">
+      <c r="A41" s="21">
         <v>40</v>
       </c>
-      <c r="B41" s="28">
+      <c r="B41" s="23">
         <v>8</v>
       </c>
-      <c r="C41" s="28">
+      <c r="C41" s="23">
         <v>-2.87E-2</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="26">
+      <c r="A42" s="21">
         <v>41</v>
       </c>
-      <c r="B42" s="28">
+      <c r="B42" s="23">
         <v>8</v>
       </c>
-      <c r="C42" s="28">
+      <c r="C42" s="23">
         <v>1.6299999999999999E-2</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="26">
+      <c r="A43" s="21">
         <v>42</v>
       </c>
-      <c r="B43" s="28">
+      <c r="B43" s="23">
         <v>9</v>
       </c>
-      <c r="C43" s="28">
+      <c r="C43" s="23">
         <v>-0.14499999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="26">
+      <c r="A44" s="21">
         <v>43</v>
       </c>
-      <c r="B44" s="28">
+      <c r="B44" s="23">
         <v>9</v>
       </c>
-      <c r="C44" s="28">
+      <c r="C44" s="23">
         <v>-0.1</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="26">
+      <c r="A45" s="21">
         <v>44</v>
       </c>
-      <c r="B45" s="28">
+      <c r="B45" s="23">
         <v>9</v>
       </c>
-      <c r="C45" s="28">
+      <c r="C45" s="23">
         <v>-5.5E-2</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="26">
+      <c r="A46" s="21">
         <v>45</v>
       </c>
-      <c r="B46" s="28">
+      <c r="B46" s="23">
         <v>9</v>
       </c>
-      <c r="C46" s="28">
+      <c r="C46" s="23">
         <v>-0.01</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="26">
+      <c r="A47" s="21">
         <v>46</v>
       </c>
-      <c r="B47" s="28">
+      <c r="B47" s="23">
         <v>9</v>
       </c>
-      <c r="C47" s="28">
+      <c r="C47" s="23">
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="26">
+      <c r="A48" s="21">
         <v>47</v>
       </c>
-      <c r="B48" s="28">
+      <c r="B48" s="23">
         <v>10</v>
       </c>
-      <c r="C48" s="28">
+      <c r="C48" s="23">
         <v>-0.1263</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="26">
+      <c r="A49" s="21">
         <v>48</v>
       </c>
-      <c r="B49" s="28">
+      <c r="B49" s="23">
         <v>10</v>
       </c>
-      <c r="C49" s="28">
+      <c r="C49" s="23">
         <v>-8.1299999999999997E-2</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="26">
+      <c r="A50" s="21">
         <v>49</v>
       </c>
-      <c r="B50" s="28">
+      <c r="B50" s="23">
         <v>10</v>
       </c>
-      <c r="C50" s="28">
+      <c r="C50" s="23">
         <v>-3.6299999999999999E-2</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="26">
+      <c r="A51" s="21">
         <v>50</v>
       </c>
-      <c r="B51" s="28">
+      <c r="B51" s="23">
         <v>10</v>
       </c>
-      <c r="C51" s="28">
+      <c r="C51" s="23">
         <v>8.6999999999999994E-3</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="26">
+      <c r="A52" s="21">
         <v>51</v>
       </c>
-      <c r="B52" s="28">
+      <c r="B52" s="23">
         <v>10</v>
       </c>
-      <c r="C52" s="28">
+      <c r="C52" s="23">
         <v>5.3699999999999998E-2</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="26">
+      <c r="A53" s="21">
         <v>52</v>
       </c>
-      <c r="B53" s="28">
+      <c r="B53" s="23">
         <v>11</v>
       </c>
-      <c r="C53" s="28">
+      <c r="C53" s="23">
         <v>-0.1075</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="26">
+      <c r="A54" s="21">
         <v>53</v>
       </c>
-      <c r="B54" s="28">
+      <c r="B54" s="23">
         <v>11</v>
       </c>
-      <c r="C54" s="28">
+      <c r="C54" s="23">
         <v>-6.25E-2</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="26">
+      <c r="A55" s="21">
         <v>54</v>
       </c>
-      <c r="B55" s="28">
+      <c r="B55" s="23">
         <v>11</v>
       </c>
-      <c r="C55" s="28">
+      <c r="C55" s="23">
         <v>-1.7500000000000002E-2</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="26">
+      <c r="A56" s="21">
         <v>55</v>
       </c>
-      <c r="B56" s="28">
+      <c r="B56" s="23">
         <v>11</v>
       </c>
-      <c r="C56" s="28">
+      <c r="C56" s="23">
         <v>2.75E-2</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="26">
+      <c r="A57" s="21">
         <v>56</v>
       </c>
-      <c r="B57" s="28">
+      <c r="B57" s="23">
         <v>11</v>
       </c>
-      <c r="C57" s="28">
+      <c r="C57" s="23">
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="26">
+      <c r="A58" s="21">
         <v>57</v>
       </c>
-      <c r="B58" s="28">
+      <c r="B58" s="23">
         <v>12</v>
       </c>
-      <c r="C58" s="28">
+      <c r="C58" s="23">
         <v>-8.8800000000000004E-2</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="26">
+      <c r="A59" s="21">
         <v>58</v>
       </c>
-      <c r="B59" s="28">
+      <c r="B59" s="23">
         <v>12</v>
       </c>
-      <c r="C59" s="28">
+      <c r="C59" s="23">
         <v>-4.3799999999999999E-2</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="26">
+      <c r="A60" s="21">
         <v>59</v>
       </c>
-      <c r="B60" s="28">
+      <c r="B60" s="23">
         <v>12</v>
       </c>
-      <c r="C60" s="28">
+      <c r="C60" s="23">
         <v>1.1999999999999999E-3</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="26">
+      <c r="A61" s="21">
         <v>60</v>
       </c>
-      <c r="B61" s="28">
+      <c r="B61" s="23">
         <v>12</v>
       </c>
-      <c r="C61" s="28">
+      <c r="C61" s="23">
         <v>4.6199999999999998E-2</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="26">
+      <c r="A62" s="21">
         <v>61</v>
       </c>
-      <c r="B62" s="28">
+      <c r="B62" s="23">
         <v>12</v>
       </c>
-      <c r="C62" s="28">
+      <c r="C62" s="23">
         <v>9.1200000000000003E-2</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="26">
+      <c r="A63" s="21">
         <v>62</v>
       </c>
-      <c r="B63" s="28">
+      <c r="B63" s="23">
         <v>13</v>
       </c>
-      <c r="C63" s="28">
+      <c r="C63" s="23">
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="26">
+      <c r="A64" s="21">
         <v>63</v>
       </c>
-      <c r="B64" s="28">
+      <c r="B64" s="23">
         <v>13</v>
       </c>
-      <c r="C64" s="28">
+      <c r="C64" s="23">
         <v>-2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="26">
+      <c r="A65" s="21">
         <v>64</v>
       </c>
-      <c r="B65" s="28">
+      <c r="B65" s="23">
         <v>13</v>
       </c>
-      <c r="C65" s="28">
+      <c r="C65" s="23">
         <v>0.02</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="26">
+      <c r="A66" s="21">
         <v>65</v>
       </c>
-      <c r="B66" s="28">
+      <c r="B66" s="23">
         <v>13</v>
       </c>
-      <c r="C66" s="28">
+      <c r="C66" s="23">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="26">
+      <c r="A67" s="21">
         <v>66</v>
       </c>
-      <c r="B67" s="28">
+      <c r="B67" s="23">
         <v>13</v>
       </c>
-      <c r="C67" s="28">
+      <c r="C67" s="23">
         <v>0.11</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="26">
+      <c r="A68" s="21">
         <v>67</v>
       </c>
-      <c r="B68" s="28">
+      <c r="B68" s="23">
         <v>14</v>
       </c>
-      <c r="C68" s="28">
+      <c r="C68" s="23">
         <v>-5.1299999999999998E-2</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="26">
+      <c r="A69" s="21">
         <v>68</v>
       </c>
-      <c r="B69" s="28">
+      <c r="B69" s="23">
         <v>14</v>
       </c>
-      <c r="C69" s="28">
+      <c r="C69" s="23">
         <v>-6.3E-3</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="26">
+      <c r="A70" s="21">
         <v>69</v>
       </c>
-      <c r="B70" s="28">
+      <c r="B70" s="23">
         <v>14</v>
       </c>
-      <c r="C70" s="28">
+      <c r="C70" s="23">
         <v>3.8699999999999998E-2</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="26">
+      <c r="A71" s="21">
         <v>70</v>
       </c>
-      <c r="B71" s="28">
+      <c r="B71" s="23">
         <v>14</v>
       </c>
-      <c r="C71" s="28">
+      <c r="C71" s="23">
         <v>8.3699999999999997E-2</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="26">
+      <c r="A72" s="21">
         <v>71</v>
       </c>
-      <c r="B72" s="28">
+      <c r="B72" s="23">
         <v>14</v>
       </c>
-      <c r="C72" s="28">
+      <c r="C72" s="23">
         <v>0.12870000000000001</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="26">
+      <c r="A73" s="21">
         <v>72</v>
       </c>
-      <c r="B73" s="28">
+      <c r="B73" s="23">
         <v>15</v>
       </c>
-      <c r="C73" s="28">
+      <c r="C73" s="23">
         <v>-3.2500000000000001E-2</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="26">
+      <c r="A74" s="21">
         <v>73</v>
       </c>
-      <c r="B74" s="28">
+      <c r="B74" s="23">
         <v>15</v>
       </c>
-      <c r="C74" s="28">
+      <c r="C74" s="23">
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="26">
+      <c r="A75" s="21">
         <v>74</v>
       </c>
-      <c r="B75" s="28">
+      <c r="B75" s="23">
         <v>15</v>
       </c>
-      <c r="C75" s="28">
+      <c r="C75" s="23">
         <v>5.7500000000000002E-2</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="26">
+      <c r="A76" s="21">
         <v>75</v>
       </c>
-      <c r="B76" s="28">
+      <c r="B76" s="23">
         <v>15</v>
       </c>
-      <c r="C76" s="28">
+      <c r="C76" s="23">
         <v>0.10249999999999999</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="26">
+      <c r="A77" s="21">
         <v>76</v>
       </c>
-      <c r="B77" s="28">
+      <c r="B77" s="23">
         <v>15</v>
       </c>
-      <c r="C77" s="28">
+      <c r="C77" s="23">
         <v>0.14749999999999999</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="26">
+      <c r="A78" s="21">
         <v>77</v>
       </c>
-      <c r="B78" s="28">
+      <c r="B78" s="23">
         <v>16</v>
       </c>
-      <c r="C78" s="28">
+      <c r="C78" s="23">
         <v>-1.37E-2</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="26">
+      <c r="A79" s="21">
         <v>78</v>
       </c>
-      <c r="B79" s="28">
+      <c r="B79" s="23">
         <v>16</v>
       </c>
-      <c r="C79" s="28">
+      <c r="C79" s="23">
         <v>3.1199999999999999E-2</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="26">
+      <c r="A80" s="21">
         <v>79</v>
       </c>
-      <c r="B80" s="28">
+      <c r="B80" s="23">
         <v>16</v>
       </c>
-      <c r="C80" s="28">
+      <c r="C80" s="23">
         <v>7.6200000000000004E-2</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="26">
+      <c r="A81" s="21">
         <v>80</v>
       </c>
-      <c r="B81" s="28">
+      <c r="B81" s="23">
         <v>16</v>
       </c>
-      <c r="C81" s="28">
+      <c r="C81" s="23">
         <v>0.1212</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="26">
+      <c r="A82" s="21">
         <v>81</v>
       </c>
-      <c r="B82" s="28">
+      <c r="B82" s="23">
         <v>16</v>
       </c>
-      <c r="C82" s="28">
+      <c r="C82" s="23">
         <v>0.1663</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="26">
+      <c r="A83" s="21">
         <v>82</v>
       </c>
-      <c r="B83" s="28">
+      <c r="B83" s="23">
         <v>17</v>
       </c>
-      <c r="C83" s="28">
+      <c r="C83" s="23">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="26">
+      <c r="A84" s="21">
         <v>83</v>
       </c>
-      <c r="B84" s="28">
+      <c r="B84" s="23">
         <v>17</v>
       </c>
-      <c r="C84" s="28">
+      <c r="C84" s="23">
         <v>0.05</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="26">
+      <c r="A85" s="21">
         <v>84</v>
       </c>
-      <c r="B85" s="28">
+      <c r="B85" s="23">
         <v>17</v>
       </c>
-      <c r="C85" s="28">
+      <c r="C85" s="23">
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="26">
+      <c r="A86" s="21">
         <v>85</v>
       </c>
-      <c r="B86" s="28">
+      <c r="B86" s="23">
         <v>17</v>
       </c>
-      <c r="C86" s="28">
+      <c r="C86" s="23">
         <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="26">
+      <c r="A87" s="21">
         <v>86</v>
       </c>
-      <c r="B87" s="28">
+      <c r="B87" s="23">
         <v>17</v>
       </c>
-      <c r="C87" s="28">
+      <c r="C87" s="23">
         <v>0.185</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="26">
+      <c r="A88" s="21">
         <v>87</v>
       </c>
-      <c r="B88" s="28">
+      <c r="B88" s="23">
         <v>18</v>
       </c>
-      <c r="C88" s="28">
+      <c r="C88" s="23">
         <v>2.3699999999999999E-2</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="26">
+      <c r="A89" s="21">
         <v>88</v>
       </c>
-      <c r="B89" s="28">
+      <c r="B89" s="23">
         <v>18</v>
       </c>
-      <c r="C89" s="28">
+      <c r="C89" s="23">
         <v>6.8699999999999997E-2</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="26">
+      <c r="A90" s="21">
         <v>89</v>
       </c>
-      <c r="B90" s="28">
+      <c r="B90" s="23">
         <v>18</v>
       </c>
-      <c r="C90" s="28">
+      <c r="C90" s="23">
         <v>0.1137</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="26">
+      <c r="A91" s="21">
         <v>90</v>
       </c>
-      <c r="B91" s="28">
+      <c r="B91" s="23">
         <v>18</v>
       </c>
-      <c r="C91" s="28">
+      <c r="C91" s="23">
         <v>0.15870000000000001</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="26">
+      <c r="A92" s="21">
         <v>91</v>
       </c>
-      <c r="B92" s="28">
+      <c r="B92" s="23">
         <v>18</v>
       </c>
-      <c r="C92" s="28">
+      <c r="C92" s="23">
         <v>0.20369999999999999</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="26">
+      <c r="A93" s="21">
         <v>92</v>
       </c>
-      <c r="B93" s="28">
+      <c r="B93" s="23">
         <v>19</v>
       </c>
-      <c r="C93" s="28">
+      <c r="C93" s="23">
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="26">
+      <c r="A94" s="21">
         <v>93</v>
       </c>
-      <c r="B94" s="28">
+      <c r="B94" s="23">
         <v>19</v>
       </c>
-      <c r="C94" s="28">
+      <c r="C94" s="23">
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="26">
+      <c r="A95" s="21">
         <v>94</v>
       </c>
-      <c r="B95" s="28">
+      <c r="B95" s="23">
         <v>19</v>
       </c>
-      <c r="C95" s="28">
+      <c r="C95" s="23">
         <v>0.13250000000000001</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="26">
+      <c r="A96" s="21">
         <v>95</v>
       </c>
-      <c r="B96" s="28">
+      <c r="B96" s="23">
         <v>19</v>
       </c>
-      <c r="C96" s="28">
+      <c r="C96" s="23">
         <v>0.17749999999999999</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="26">
+      <c r="A97" s="21">
         <v>96</v>
       </c>
-      <c r="B97" s="28">
+      <c r="B97" s="23">
         <v>19</v>
       </c>
-      <c r="C97" s="28">
+      <c r="C97" s="23">
         <v>0.2225</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="26">
+      <c r="A98" s="21">
         <v>97</v>
       </c>
-      <c r="B98" s="28">
+      <c r="B98" s="23">
         <v>20</v>
       </c>
-      <c r="C98" s="28">
+      <c r="C98" s="23">
         <v>6.1199999999999997E-2</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A99" s="26">
+      <c r="A99" s="21">
         <v>98</v>
       </c>
-      <c r="B99" s="28">
+      <c r="B99" s="23">
         <v>20</v>
       </c>
-      <c r="C99" s="28">
+      <c r="C99" s="23">
         <v>0.1062</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="26">
+      <c r="A100" s="21">
         <v>99</v>
       </c>
-      <c r="B100" s="28">
+      <c r="B100" s="23">
         <v>20</v>
       </c>
-      <c r="C100" s="28">
+      <c r="C100" s="23">
         <v>0.1512</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="26">
+      <c r="A101" s="21">
         <v>100</v>
       </c>
-      <c r="B101" s="28">
+      <c r="B101" s="23">
         <v>20</v>
       </c>
-      <c r="C101" s="28">
+      <c r="C101" s="23">
         <v>0.19620000000000001</v>
       </c>
     </row>
